--- a/AWS_Cloud Practitioner勉強.xlsx
+++ b/AWS_Cloud Practitioner勉強.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1D7AA5-7A39-455B-B718-B181D2C1D428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DB10FF-14B2-4788-895E-610DFBAD8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Service" sheetId="1" r:id="rId1"/>
-    <sheet name="メッセージングサービス" sheetId="2" r:id="rId2"/>
+    <sheet name="AWSのインターネットインフラ" sheetId="3" r:id="rId2"/>
+    <sheet name="DB&amp;Storage" sheetId="4" r:id="rId3"/>
+    <sheet name="監視" sheetId="5" r:id="rId4"/>
+    <sheet name="メッセージングサービス" sheetId="2" r:id="rId5"/>
+    <sheet name="コスト関連" sheetId="6" r:id="rId6"/>
+    <sheet name="移行" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,11 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
-  <si>
-    <t>Elastic Load Balancing</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <r>
       <t>中国語：</t>
@@ -67,73 +68,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Amazon Elastic Container Service</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ECS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Amazon Elastic Kubernetes Service</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>EKS（K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S）</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>AWS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Fargate</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>Fargate：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>拦截</t>
-    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -212,6 +147,1357 @@
   </si>
   <si>
     <t>AWS Lambda</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>簡単に言うと「インターネット上で使える仮想マシン（サーバー）」を必要なときにすぐ作って、好きなときに削除できるクラウドサービスです。</t>
+  </si>
+  <si>
+    <t>EC2は、AWS（Amazon Web Services）が提供する仮想サーバーサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Elastic Compute Cloud（EC2）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Elastic Load Balancing（ELB）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ELBは、AWSの負荷分散サービスで、複数のEC2インスタンスなどにトラフィックを自動で分散させて、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高可用性・スケーラビリティ・耐障害性を実現します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>AWS Lambda（ラムダ）は、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サーバーの管理不要でコードを実行できるサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「サーバーレスコンピューティング」と呼ばれる仕組みの代表で、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>イベント駆動で処理を自動実行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>できるのが最大の特長です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Elastic Container Service（ECS）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>ECSは、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dockerコンテナを簡単にデプロイ・管理できるAWSのコンテナオーケストレーションサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>サーバーやクラスタの管理を最小限に抑えつつ、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本番環境でも安定してコンテナを動かせる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のが大きなメリットです。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>EKS（K8S）は</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kubernetesクラスタを簡単にAWS上で使えるようにするマネージドサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「Kubernetes（K8s）」を自分で構築・運用せずに、AWS が代わりにやってくれるサービス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EC2インスタンスを管理せずに、必要なCPUとメモリだけ指定すればコンテナが動くという、非常にシンプルで効率的な仕組みです。</t>
+  </si>
+  <si>
+    <t>AWS Fargate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Fargate（ファーゲート）は、サーバーレスでコンテナを実行できるAWSのサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>无服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>器容器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>算引擎</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>サーバーレス：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无服务器的</t>
+    </r>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SQSは、分散システム間でメッセージ（命令・データ）を非同期にやりとりするためのキューサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>キューサービス：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>队列服务</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>AWS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Simple Queue Service（SQS）</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>AWS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Simple Notification Service（SNS）</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SNSは、アプリケーション間やシステム利用者に向けて、メッセージをリアルタイムでプッシュ配信するための通知サービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プッシュ配信する：推送</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>关键业务因素：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合规性</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>接近度</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>功能可用性</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>定价</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>符合当地的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>相关法律法规</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>服务器地点和业务发生地之间的距离</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>附近的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节点是否可以提供相关功能</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>根据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实际情况产生的成本</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Management Console</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon CloudFront</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Route 53</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Outposts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Elastic Beantalk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主に、ウェブサイトやアプリケーションの静的・動的コンテンツを高速・安全・グローバルに配信するために使用されます。</t>
+  </si>
+  <si>
+    <r>
+      <t>Amazon CloudFrontは、AWS（Amazon Web Services）の</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提供するコンテンツ配信ネットワーク（CDN）サービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界中のユーザーに高速・安定して配信するための分散ネットワークシステムです。</t>
+  </si>
+  <si>
+    <t>CDN（Content Delivery Network）とは、Webサイトやアプリの画像・動画・HTML・CSS・JSなどのコンテンツを、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CDN：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>Amazon Route 53は、AWSが</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提供するスケーラブルで高可用性なDNS（ドメインネームシステム）ウェブサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DNS：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「人間が読みやすいドメイン名（例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>www.example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を、機械が理解できる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドレス（例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>192.0.2.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）に変換する仕組み」です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>AWS のインフラやサービスを、お客様のオンプレミス（自社データセンターなど）に設置して利用できる</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ハイブリッドクラウドソリューション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（混合云解决方案）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WebアプリケーションやAPIを簡単にデプロイ・スケーリング・管理できる、完全マネージド型のPaaS（Platform as a Service）です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>デプロイ・スケーリング：部署・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扩展</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「開発者がアプリに集中できるように、OSやサーバー、ネットワークなどの面倒な部分をクラウド事業者が全部用意・管理してくれる」サービスです。</t>
+  </si>
+  <si>
+    <t>※PaaSとは：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS のすべてのサービスをブラウザ上で視覚的に操作・管理できるウェブインターフェースです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS CLI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ターミナルやコマンドプロンプトからAWSを操作できるツール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Python、JavaScript、JavaなどのプログラムからAWSを操作できるライブラリ群</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hybrid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Virtual Private Cloud（Amazon VPC）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS上に自分専用の仮想ネットワーク空間を作れるサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンプレミスでいう「自社ネットワーク」のようなものを、AWSクラウド上に構築できます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Direct Connect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>オンプレミス（自社データセンター）とAWSを</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>専用線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>で直接接続するネットワークサービスです。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デメリット：費用が高い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWSのセキュリティグループとACL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon DocumentDB(with MongoDB compatibility)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Managed Blockchain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Quantum Ledger Database(Amazon QLDB)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon ElastiCache</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon DynamoDB Accelerator(DAX)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JSON形式のドキュメントデータを扱うデータベースでありながら、MongoDB互換APIを提供することで、</t>
+  </si>
+  <si>
+    <t>MongoDBを使っていたアプリケーションをほぼそのまま移行できるようにしたフルマネージド型のドキュメントデータベースサービスです。</t>
+  </si>
+  <si>
+    <t>グラフデータベース（Graph Database）をフルマネージドで提供するサービスで、人やモノ、場所などの「関係性（リレーション）」を扱うのに最適です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Neptune(SNSアプリに向け)</t>
+    <rPh sb="22" eb="23">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>フルマネージド：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全托管</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hyperledger FabricやEthereumなどの人気のブロックチェーンフレームワークをサポートしています。</t>
+  </si>
+  <si>
+    <t>ブロックチェーンネットワーク（分散型台帳）を簡単に構築・管理できるフルマネージドサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>ブロックチェーン：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>区块链</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金融機関向け</t>
+    <rPh sb="4" eb="5">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一般的なデータベースと異なり、すべての変更履歴が自動的に保持・検証可能で、信頼性の高いデータトレーサビリティ（追跡性）を実現します。</t>
+  </si>
+  <si>
+    <r>
+      <t>金融機関などで求められる「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>完全で改ざん不可能なトランザクション履歴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」を記録するための</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>台帳型データベースサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インメモリキャッシュ（RAM上の高速データベース）をAWSで簡単に使えるようにしたフルマネージドサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RedisとMemcachedという2つの人気オープンソースエンジンに対応しており、アプリケーションのレスポンス性能を劇的に向上させることができます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon DAX（DynamoDB Accelerator）は、DynamoDBの読み取り性能を最大10倍高速化するためのインメモリキャッシュサービスです。</t>
+  </si>
+  <si>
+    <r>
+      <t>ElastiCacheのような汎用キャッシュとは異なり、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DynamoDB専用に設計されたフルマネージドなキャッシュレイヤー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Elastic Block Store(EBS)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮想ハードディスクのようなものと考えるとわかりやすいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>EC2インスタンスにアタッチして使う</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高性能ブロックストレージ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NoSQL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数のEC2インスタンスで共有できるスケーラブルなNFS（Network File System）準拠のファイルストレージサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Elastic File System（EFS）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Redshift</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SQLベースで使えるため、従来のRDB経験者でもすぐに使え、BIツールやETLともスムーズに統合可能です。</t>
+  </si>
+  <si>
+    <t>ペタバイト級のデータ分析を高速に処理できるフルマネージド型のデータウェアハウスサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペタバイト：1PB=1024TB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Relational Database Service(RDS)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Aurora</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>リレーショナルデータベース（RDB）を</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フルマネージドで利用できるサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MySQLおよびPostgreSQL互換のリレーショナルデータベースで、商用DBと同等の性能・可用性を、オープンソースDBのコストで提供するAWS独自の高性能DBサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Simple Storage Service(Amazon S3)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon S3 Glacier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Database Migration Service(DMS)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Schema Conversion Tool</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像・動画・ログ・バックアップなど、あらゆるデータを保存・配信・共有可能です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>任意の量のデータを安全・スケーラブルに保存できる</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>オブジェクトストレージサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アクセス頻度が非常に低いデータを長期保管するための低コストなストレージクラス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>法令・監査・バックアップなどで「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>今は使わないが、数年後に必要になる可能性のあるデータ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」を保存するのに最適です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンプレミスや他のクラウド上のデータベースを、AWS上のデータベースに安全かつリアルタイムで移行できるマネージドサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>移行中も元のデータベースを稼働させたまま移行可能なため、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ダウンタイムを最小化した移行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が可能です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異なるデータベース間のスキーマ（構造）やSQLコードを自動で変換するための無料デスクトップアプリケーションです。</t>
+  </si>
+  <si>
+    <t>特に「異種DB間の移行（例：Oracle → PostgreSQL、SQL Server → Aurora）」で非常に重要な役割を果たします。</t>
+  </si>
+  <si>
+    <t>AWS CloudTrail</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Trusted Advisor</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon CloudWatch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWSリソースやアプリケーションの監視サービスです。CPU使用率やネットワークトラフィック、ログなどを収集・表示・アラート通知できます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS環境のベストプラクティスチェックを自動で行うサポートツールです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWSアカウント内でのAPI操作を記録・監査するサービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誰が・いつ・どのサービスで・何をしたのかを追跡できます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Cost Explorer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Marketplace</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS VMware Cloud</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon SageMaker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Augemented AI(Amazon A2I)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Lex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Textract</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon DeepRacer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Ground Station</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VMwareとAmazon Web Services（AWS）が共同開発したクラウドサービスです。</t>
+  </si>
+  <si>
+    <t>オンプレミス（自社サーバー）で利用しているVMwareの仮想化環境（vSphere, vSAN, NSXなど）を、そのままAWSクラウド上に移行・拡張できるようにするためのソリューションです。</t>
+  </si>
+  <si>
+    <t>AWSが提供するフルマネージドの機械学習（ML）サービスです。</t>
+  </si>
+  <si>
+    <t>機械学習モデルの構築・トレーニング・デプロイ（本番運用）まで、すべてを一貫して実行できる環境を提供します。</t>
+  </si>
+  <si>
+    <t>機械学習モデルの判断を人間が補完（人手で確認・修正）できる仕組みを提供するAWSサービスです。</t>
+  </si>
+  <si>
+    <t>特に、AIの予測結果に不確実性がある場合や、重要な判断を人間の目でもチェックしたいときに活用されます。</t>
+  </si>
+  <si>
+    <t>音声およびテキストによる対話型インターフェース（チャットボット）を構築できる、AWSが提供する自然言語処理（NLP）サービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキャン画像やPDFからテキスト・表・フォームの情報を自動で抽出する、AWSのOCR（光学文字認識）サービスです。</t>
+  </si>
+  <si>
+    <t>通常のOCRと違い、Textractは文書構造（テーブル・フォーム・キーと値など）を理解して抽出できるのが最大の特徴です。</t>
+  </si>
+  <si>
+    <t>AWSが提供する「強化学習（Reinforcement Learning）を楽しく学ぶための小型自動運転カー＆シミュレータ＋競技プラットフォーム」です。</t>
+  </si>
+  <si>
+    <t>実際のミニカーを使ったり、仮想シミュレータで自動運転モデルを訓練・競技させたりすることで、機械学習（特に強化学習）の実践力を学べます。</t>
+  </si>
+  <si>
+    <t>AWSが提供する「地球観測衛星と通信するための地上局（アンテナ）」をクラウド経由で使えるサービスです。</t>
+  </si>
+  <si>
+    <t>これにより、人工衛星から送られてくるデータをクラウド上で即座に受信・処理・保存・分析できるようになります。</t>
+  </si>
+  <si>
+    <t>AWS CAF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>企業がクラウド導入・活用を成功させるための</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ガイドラインとベストプラクティスのフレームワーク</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>プラクティス：Practice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实践</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Snowone</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Snowball Edge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS Snowmobile</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフラインでもクラウドへのデータ移行や処理が可能で、過酷な環境や遠隔地でも活用されます。</t>
+  </si>
+  <si>
+    <r>
+      <t>AWSが提供する「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ポータブルで耐久性が高い、超小型データ転送＆エッジコンピューティングデバイス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」です。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポータブル：便携的</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大量のデータを安全かつ効率的にAWSクラウドに移行したり、エッジ環境でローカル処理（AI・分析）を実行できる堅牢なポータブルデバイスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際のトレーラー（40フィートの輸送トラック）を使い、データセンター全体の移行など超大規模なケースに特化しています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大100ペタバイト（PB）のデータを物理的にAWSクラウドに移行できる、コンテナ型データ移送サービスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS（Amazon Web Services）での利用料金と使用状況を視覚的に分析・管理できるツールです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業や個人がクラウドの支出を最適化するために非常に役立ちます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Web Services（AWS）上で利用できるソフトウェアやサービスを簡単に探して導入できるオンラインストアです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業向けのITソリューションを中心に、サードパーティ（外部企業）やAWS自身が提供する製品が多数掲載されています。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -219,7 +1505,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +1534,29 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -269,9 +1578,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -292,6 +1613,99 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>25822</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>168646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723B305F-F13E-441E-A0C0-D729E57FAE69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="2286000"/>
+          <a:ext cx="7569622" cy="7217146"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>168686</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>40465</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE1728FB-537E-47A0-B097-C08B7BC7D52F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7753350" y="2286000"/>
+          <a:ext cx="7502936" cy="3278965"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -329,6 +1743,55 @@
         <a:xfrm>
           <a:off x="209550" y="1524000"/>
           <a:ext cx="8024503" cy="3174173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>151336</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>74652</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F337BAC-4F9D-29A2-348C-9372FD89B811}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="419101" y="762001"/>
+          <a:ext cx="6018735" cy="2551151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -603,80 +2066,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:C21"/>
+  <dimension ref="B2:AI37"/>
   <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="2.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="15" customHeight="1">
+    <row r="2" spans="2:20" ht="15" customHeight="1">
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="15" customHeight="1">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="15" customHeight="1">
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="15" customHeight="1">
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" ht="15" customHeight="1">
-      <c r="C3" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="15" customHeight="1">
-      <c r="B4" s="1" t="s">
+    <row r="8" spans="2:20" ht="15" customHeight="1">
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="15" customHeight="1">
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="15" customHeight="1">
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="15" customHeight="1">
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="15" customHeight="1">
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="2:35" ht="15" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:35" ht="15" customHeight="1">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:35" ht="15" customHeight="1">
+      <c r="C19" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" ht="15" customHeight="1">
+      <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="15" customHeight="1">
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="15" customHeight="1">
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="C9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="15" customHeight="1">
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="15" customHeight="1">
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1">
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="15" customHeight="1">
-      <c r="C15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="C21" s="1" t="s">
-        <v>12</v>
+    <row r="23" spans="2:35" ht="15" customHeight="1">
+      <c r="C23" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" ht="15" customHeight="1">
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" ht="15" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" ht="15" customHeight="1">
+      <c r="C28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI28" s="2"/>
+    </row>
+    <row r="29" spans="2:35" ht="15" customHeight="1">
+      <c r="C29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="2:35" ht="15" customHeight="1">
+      <c r="B32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" ht="15" customHeight="1">
+      <c r="C33" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" ht="15" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" ht="15" customHeight="1">
+      <c r="C37" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -687,6 +2209,503 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722955EB-232D-4063-874F-47E59C788982}">
+  <dimension ref="B2:AQ52"/>
+  <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.69921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="15" customHeight="1">
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="15" customHeight="1">
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15" customHeight="1">
+      <c r="C4" s="3"/>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15" customHeight="1">
+      <c r="C5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15" customHeight="1">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15" customHeight="1">
+      <c r="C7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15" customHeight="1">
+      <c r="C8" s="3"/>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="15" customHeight="1">
+      <c r="C9" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15" customHeight="1">
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="15" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15" customHeight="1">
+      <c r="C14" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="15" customHeight="1">
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="2:43" ht="15" customHeight="1">
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:43" ht="15" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:43" ht="15" customHeight="1">
+      <c r="C20" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:43" ht="15" customHeight="1">
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:43" ht="15" customHeight="1">
+      <c r="C24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:43" ht="15" customHeight="1">
+      <c r="C25" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="2:43" ht="15" customHeight="1">
+      <c r="C26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="2:43" ht="15" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ29" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:43" ht="15" customHeight="1">
+      <c r="C30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ30" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="2:43" ht="15" customHeight="1">
+      <c r="C31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ31" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="2:43" ht="15" customHeight="1">
+      <c r="B34" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="2:43" ht="15" customHeight="1">
+      <c r="C35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AQ35" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:43" ht="15" customHeight="1">
+      <c r="AQ36" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="2:43" ht="15" customHeight="1">
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:43" ht="15" customHeight="1">
+      <c r="C39" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="2:43" ht="15" customHeight="1">
+      <c r="B42" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="2:43" ht="15" customHeight="1">
+      <c r="C43" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="2:43" ht="15" customHeight="1">
+      <c r="C44" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="2:43" ht="15" customHeight="1">
+      <c r="B47" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="2:43" ht="15" customHeight="1">
+      <c r="C48" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="15" customHeight="1">
+      <c r="D49" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="15" customHeight="1">
+      <c r="B52" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12F9E57-03B2-42AF-AB02-C984C5AD216D}">
+  <dimension ref="B2:W56"/>
+  <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.69921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" ht="15" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="15" customHeight="1">
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="15" customHeight="1">
+      <c r="C4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="15" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="15" customHeight="1">
+      <c r="C7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="15" customHeight="1">
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="15" customHeight="1">
+      <c r="C10" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="15" customHeight="1">
+      <c r="C11" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="15" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="15" customHeight="1">
+      <c r="C14" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" ht="15" customHeight="1">
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="15" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="15" customHeight="1">
+      <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="15" customHeight="1">
+      <c r="C19" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="15" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="15" customHeight="1">
+      <c r="C22" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1">
+      <c r="C23" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="15" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" ht="15" customHeight="1">
+      <c r="C26" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" ht="15" customHeight="1">
+      <c r="C27" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="15" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="15" customHeight="1">
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="15" customHeight="1">
+      <c r="B32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" ht="15" customHeight="1">
+      <c r="C33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" ht="15" customHeight="1">
+      <c r="C34" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" ht="15" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" ht="15" customHeight="1">
+      <c r="C37" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" ht="15" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" ht="15" customHeight="1">
+      <c r="C40" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" ht="15" customHeight="1">
+      <c r="B42" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" ht="15" customHeight="1">
+      <c r="C43" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" ht="15" customHeight="1">
+      <c r="C44" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" ht="15" customHeight="1">
+      <c r="B46" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" ht="15" customHeight="1">
+      <c r="C47" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" ht="15" customHeight="1">
+      <c r="C48" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="15" customHeight="1">
+      <c r="B50" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="15" customHeight="1">
+      <c r="B51" s="3"/>
+      <c r="C51" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="15" customHeight="1">
+      <c r="B52" s="3"/>
+      <c r="C52" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="15" customHeight="1">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" ht="15" customHeight="1">
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15" customHeight="1">
+      <c r="C55" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="15" customHeight="1">
+      <c r="C56" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EAC488C-4104-4F86-ADD9-97544D1D3B0D}">
+  <dimension ref="B2:C10"/>
+  <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.69921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15" customHeight="1">
+      <c r="C3" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15" customHeight="1">
+      <c r="C4" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15" customHeight="1">
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1">
+      <c r="B9" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15" customHeight="1">
+      <c r="C10" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F490B73-C6A6-4D8A-9149-91707EB51350}">
   <dimension ref="B2:N6"/>
   <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
@@ -696,28 +2715,28 @@
   <sheetData>
     <row r="2" spans="2:14" ht="15" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="15" customHeight="1">
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -725,4 +2744,224 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A605FE9-45AA-441B-9D8C-98D6BB6CB3C8}">
+  <dimension ref="B2:AC43"/>
+  <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.69921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15" customHeight="1">
+      <c r="C3" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15" customHeight="1">
+      <c r="C4" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15" customHeight="1">
+      <c r="C21" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15" customHeight="1">
+      <c r="C22" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="29:29" ht="15" customHeight="1">
+      <c r="AC43" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616545FB-A2D5-4C04-9881-1C5BF3F5D298}">
+  <dimension ref="B2:H41"/>
+  <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.69921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15" customHeight="1">
+      <c r="C3" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15" customHeight="1">
+      <c r="C4" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15" customHeight="1">
+      <c r="C7" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="15" customHeight="1">
+      <c r="C8" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15" customHeight="1">
+      <c r="B10" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="15" customHeight="1">
+      <c r="C11" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="15" customHeight="1">
+      <c r="C12" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15" customHeight="1">
+      <c r="B14" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15" customHeight="1">
+      <c r="C15" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="15" customHeight="1">
+      <c r="C18" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15" customHeight="1">
+      <c r="C19" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="15" customHeight="1">
+      <c r="C22" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="15" customHeight="1">
+      <c r="C23" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="15" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="15" customHeight="1">
+      <c r="C26" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="15" customHeight="1">
+      <c r="C27" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="15" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="15" customHeight="1">
+      <c r="C30" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="15" customHeight="1">
+      <c r="B32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="15" customHeight="1">
+      <c r="C33" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="15" customHeight="1">
+      <c r="C34" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="15" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="15" customHeight="1">
+      <c r="C37" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="15" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="15" customHeight="1">
+      <c r="C40" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="15" customHeight="1">
+      <c r="C41" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>